--- a/dynamical_DE_nonfid/data/combined/cmb+pelg+jmul-w0wacdm-free.xlsx
+++ b/dynamical_DE_nonfid/data/combined/cmb+pelg+jmul-w0wacdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39281941.52460233</v>
+        <v>38939111.63836218</v>
       </c>
       <c r="C2" t="n">
-        <v>-134153351.8096211</v>
+        <v>-132260495.2777102</v>
       </c>
       <c r="D2" t="n">
-        <v>40313641.33154508</v>
+        <v>40043373.18061995</v>
       </c>
       <c r="E2" t="n">
-        <v>-342126.7590768026</v>
+        <v>-304071.7046410501</v>
       </c>
       <c r="F2" t="n">
-        <v>-1328975.273592839</v>
+        <v>-1328093.301861825</v>
       </c>
       <c r="G2" t="n">
-        <v>879193.0501409222</v>
+        <v>867122.0014302366</v>
       </c>
       <c r="H2" t="n">
-        <v>-2571875.463180634</v>
+        <v>-2551061.79585407</v>
       </c>
       <c r="I2" t="n">
-        <v>5847950.522657106</v>
+        <v>5788454.701047086</v>
       </c>
       <c r="J2" t="n">
-        <v>1456404.046173134</v>
+        <v>1441567.158084726</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134153351.7669997</v>
+        <v>-132260495.2792437</v>
       </c>
       <c r="C3" t="n">
-        <v>886218786.4168658</v>
+        <v>849569865.9751449</v>
       </c>
       <c r="D3" t="n">
-        <v>-88228409.81279022</v>
+        <v>-89020380.01140434</v>
       </c>
       <c r="E3" t="n">
-        <v>15663722.81314092</v>
+        <v>13953478.73111703</v>
       </c>
       <c r="F3" t="n">
-        <v>6747394.090244408</v>
+        <v>6698082.423364607</v>
       </c>
       <c r="G3" t="n">
-        <v>-3810603.105081245</v>
+        <v>-3603290.723141015</v>
       </c>
       <c r="H3" t="n">
-        <v>7895820.251794663</v>
+        <v>7802721.050476888</v>
       </c>
       <c r="I3" t="n">
-        <v>-22849906.9567231</v>
+        <v>-22109850.83267232</v>
       </c>
       <c r="J3" t="n">
-        <v>-5680685.00682297</v>
+        <v>-5495882.108367089</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40313641.33631061</v>
+        <v>40043373.17993183</v>
       </c>
       <c r="C4" t="n">
-        <v>-88228409.87509482</v>
+        <v>-89020380.00709799</v>
       </c>
       <c r="D4" t="n">
-        <v>48619723.08908681</v>
+        <v>48195380.87571658</v>
       </c>
       <c r="E4" t="n">
-        <v>920139.6035739512</v>
+        <v>831162.2299309253</v>
       </c>
       <c r="F4" t="n">
-        <v>-940999.0488376408</v>
+        <v>-944168.1700648729</v>
       </c>
       <c r="G4" t="n">
-        <v>963630.8345330142</v>
+        <v>965194.8780708149</v>
       </c>
       <c r="H4" t="n">
-        <v>-2813262.593621374</v>
+        <v>-2794640.381151586</v>
       </c>
       <c r="I4" t="n">
-        <v>6013869.454881089</v>
+        <v>5999557.628057473</v>
       </c>
       <c r="J4" t="n">
-        <v>1497594.040494522</v>
+        <v>1494045.406073365</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-342126.7575768859</v>
+        <v>-304071.7045313646</v>
       </c>
       <c r="C5" t="n">
-        <v>15663722.80915928</v>
+        <v>13953478.73062238</v>
       </c>
       <c r="D5" t="n">
-        <v>920139.6053247345</v>
+        <v>831162.2300178834</v>
       </c>
       <c r="E5" t="n">
-        <v>1026660.642139768</v>
+        <v>875016.6180342619</v>
       </c>
       <c r="F5" t="n">
-        <v>32525.60154053582</v>
+        <v>29325.63039324812</v>
       </c>
       <c r="G5" t="n">
-        <v>-76836.26207617721</v>
+        <v>-66211.02352730592</v>
       </c>
       <c r="H5" t="n">
-        <v>-6079.806147917082</v>
+        <v>-5464.288434650711</v>
       </c>
       <c r="I5" t="n">
-        <v>-252961.5144802378</v>
+        <v>-219662.6051949891</v>
       </c>
       <c r="J5" t="n">
-        <v>-61907.6601773291</v>
+        <v>-53578.13441235192</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1328975.273816418</v>
+        <v>-1328093.302308396</v>
       </c>
       <c r="C6" t="n">
-        <v>6747394.090969514</v>
+        <v>6698082.425073916</v>
       </c>
       <c r="D6" t="n">
-        <v>-940999.0490837609</v>
+        <v>-944168.1705249334</v>
       </c>
       <c r="E6" t="n">
-        <v>32525.60154547593</v>
+        <v>29325.63041014084</v>
       </c>
       <c r="F6" t="n">
-        <v>633183.2237893753</v>
+        <v>632933.8566111278</v>
       </c>
       <c r="G6" t="n">
-        <v>102903.920067268</v>
+        <v>103152.3496587172</v>
       </c>
       <c r="H6" t="n">
-        <v>41787.75448755275</v>
+        <v>41814.67440470694</v>
       </c>
       <c r="I6" t="n">
-        <v>-16774.98799652706</v>
+        <v>-15961.90737157771</v>
       </c>
       <c r="J6" t="n">
-        <v>-3782.234674641998</v>
+        <v>-3578.90421462068</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>879193.0499400873</v>
+        <v>867122.0012804061</v>
       </c>
       <c r="C7" t="n">
-        <v>-3810603.105898595</v>
+        <v>-3603290.722517366</v>
       </c>
       <c r="D7" t="n">
-        <v>963630.8341477722</v>
+        <v>965194.8779405054</v>
       </c>
       <c r="E7" t="n">
-        <v>-76836.26212368117</v>
+        <v>-66211.02352569906</v>
       </c>
       <c r="F7" t="n">
-        <v>102903.9200749365</v>
+        <v>103152.349674764</v>
       </c>
       <c r="G7" t="n">
-        <v>66230.82863565376</v>
+        <v>64930.12376743408</v>
       </c>
       <c r="H7" t="n">
-        <v>-70607.63784016088</v>
+        <v>-69962.77167174855</v>
       </c>
       <c r="I7" t="n">
-        <v>209645.4664188708</v>
+        <v>205013.4037904658</v>
       </c>
       <c r="J7" t="n">
-        <v>52549.27605351634</v>
+        <v>51392.63156420732</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2571875.46323737</v>
+        <v>-2551061.795805831</v>
       </c>
       <c r="C8" t="n">
-        <v>7895820.254961128</v>
+        <v>7802721.05018572</v>
       </c>
       <c r="D8" t="n">
-        <v>-2813262.593350376</v>
+        <v>-2794640.381149374</v>
       </c>
       <c r="E8" t="n">
-        <v>-6079.806041695538</v>
+        <v>-5464.288428942275</v>
       </c>
       <c r="F8" t="n">
-        <v>41787.75447191503</v>
+        <v>41814.67437393203</v>
       </c>
       <c r="G8" t="n">
-        <v>-70607.63785618037</v>
+        <v>-69962.77168035094</v>
       </c>
       <c r="H8" t="n">
-        <v>177105.7407924856</v>
+        <v>175727.4161489746</v>
       </c>
       <c r="I8" t="n">
-        <v>-402506.0754277812</v>
+        <v>-399143.7546658635</v>
       </c>
       <c r="J8" t="n">
-        <v>-100242.0981412822</v>
+        <v>-99404.1887000845</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5847950.52219797</v>
+        <v>5788454.700806917</v>
       </c>
       <c r="C9" t="n">
-        <v>-22849906.9624507</v>
+        <v>-22109850.83148826</v>
       </c>
       <c r="D9" t="n">
-        <v>6013869.453568889</v>
+        <v>5999557.627929104</v>
       </c>
       <c r="E9" t="n">
-        <v>-252961.514724673</v>
+        <v>-219662.6052052251</v>
       </c>
       <c r="F9" t="n">
-        <v>-16774.9879587009</v>
+        <v>-15961.90729418514</v>
       </c>
       <c r="G9" t="n">
-        <v>209645.4664370546</v>
+        <v>205013.4038077886</v>
       </c>
       <c r="H9" t="n">
-        <v>-402506.0753860215</v>
+        <v>-399143.7546576583</v>
       </c>
       <c r="I9" t="n">
-        <v>1020345.76583762</v>
+        <v>1002650.592368206</v>
       </c>
       <c r="J9" t="n">
-        <v>254278.2145003412</v>
+        <v>249861.1594954114</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1456404.046057443</v>
+        <v>1441567.158022932</v>
       </c>
       <c r="C10" t="n">
-        <v>-5680685.008248754</v>
+        <v>-5495882.108062882</v>
       </c>
       <c r="D10" t="n">
-        <v>1497594.040165799</v>
+        <v>1494045.406039651</v>
       </c>
       <c r="E10" t="n">
-        <v>-61907.66023826621</v>
+        <v>-53578.13441487408</v>
       </c>
       <c r="F10" t="n">
-        <v>-3782.234665208261</v>
+        <v>-3578.904195318219</v>
       </c>
       <c r="G10" t="n">
-        <v>52549.27605801194</v>
+        <v>51392.63156846038</v>
       </c>
       <c r="H10" t="n">
-        <v>-100242.0981307834</v>
+        <v>-99404.18869790898</v>
       </c>
       <c r="I10" t="n">
-        <v>254278.2145001442</v>
+        <v>249861.1594950863</v>
       </c>
       <c r="J10" t="n">
-        <v>63446.39183131992</v>
+        <v>62343.80485054158</v>
       </c>
     </row>
   </sheetData>

--- a/dynamical_DE_nonfid/data/combined/cmb+pelg+jmul-w0wacdm-free.xlsx
+++ b/dynamical_DE_nonfid/data/combined/cmb+pelg+jmul-w0wacdm-free.xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38939111.63836218</v>
+        <v>43676608.96314</v>
       </c>
       <c r="C2" t="n">
-        <v>-132260495.2777102</v>
+        <v>-145679194.045278</v>
       </c>
       <c r="D2" t="n">
-        <v>40043373.18061995</v>
+        <v>45466885.67214109</v>
       </c>
       <c r="E2" t="n">
-        <v>-304071.7046410501</v>
+        <v>-390768.2457246449</v>
       </c>
       <c r="F2" t="n">
-        <v>-1328093.301861825</v>
+        <v>-1323385.385501444</v>
       </c>
       <c r="G2" t="n">
-        <v>867122.0014302366</v>
+        <v>1021221.675977364</v>
       </c>
       <c r="H2" t="n">
-        <v>-2551061.79585407</v>
+        <v>-2869127.226249613</v>
       </c>
       <c r="I2" t="n">
-        <v>5788454.701047086</v>
+        <v>6563952.749624975</v>
       </c>
       <c r="J2" t="n">
-        <v>1441567.158084726</v>
+        <v>1634841.839052103</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-132260495.2792437</v>
+        <v>-145679194.0438235</v>
       </c>
       <c r="C3" t="n">
-        <v>849569865.9751449</v>
+        <v>874395433.1775708</v>
       </c>
       <c r="D3" t="n">
-        <v>-89020380.01140434</v>
+        <v>-108793551.2129388</v>
       </c>
       <c r="E3" t="n">
-        <v>13953478.73111703</v>
+        <v>16030811.12903963</v>
       </c>
       <c r="F3" t="n">
-        <v>6698082.423364607</v>
+        <v>6619107.984367039</v>
       </c>
       <c r="G3" t="n">
-        <v>-3603290.723141015</v>
+        <v>-4318637.523046921</v>
       </c>
       <c r="H3" t="n">
-        <v>7802721.050476888</v>
+        <v>8740901.746888453</v>
       </c>
       <c r="I3" t="n">
-        <v>-22109850.83267232</v>
+        <v>-25001588.99522455</v>
       </c>
       <c r="J3" t="n">
-        <v>-5495882.108367089</v>
+        <v>-6218125.940467485</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40043373.17993183</v>
+        <v>45466885.6723249</v>
       </c>
       <c r="C4" t="n">
-        <v>-89020380.00709799</v>
+        <v>-108793551.2151011</v>
       </c>
       <c r="D4" t="n">
-        <v>48195380.87571658</v>
+        <v>53579121.85202137</v>
       </c>
       <c r="E4" t="n">
-        <v>831162.2299309253</v>
+        <v>817791.112947744</v>
       </c>
       <c r="F4" t="n">
-        <v>-944168.1700648729</v>
+        <v>-961357.1764249715</v>
       </c>
       <c r="G4" t="n">
-        <v>965194.8780708149</v>
+        <v>1116645.505645147</v>
       </c>
       <c r="H4" t="n">
-        <v>-2794640.381151586</v>
+        <v>-3148827.625699731</v>
       </c>
       <c r="I4" t="n">
-        <v>5999557.628057473</v>
+        <v>6832576.364044304</v>
       </c>
       <c r="J4" t="n">
-        <v>1494045.406073365</v>
+        <v>1701453.522237655</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-304071.7045313646</v>
+        <v>-390768.2456862914</v>
       </c>
       <c r="C5" t="n">
-        <v>13953478.73062238</v>
+        <v>16030811.12893311</v>
       </c>
       <c r="D5" t="n">
-        <v>831162.2300178834</v>
+        <v>817791.1129946325</v>
       </c>
       <c r="E5" t="n">
-        <v>875016.6180342619</v>
+        <v>1106044.049117788</v>
       </c>
       <c r="F5" t="n">
-        <v>29325.63039324812</v>
+        <v>51386.66528811266</v>
       </c>
       <c r="G5" t="n">
-        <v>-66211.02352730592</v>
+        <v>-83762.11103450719</v>
       </c>
       <c r="H5" t="n">
-        <v>-5464.288434650711</v>
+        <v>-5385.10249834149</v>
       </c>
       <c r="I5" t="n">
-        <v>-219662.6051949891</v>
+        <v>-278391.2796411418</v>
       </c>
       <c r="J5" t="n">
-        <v>-53578.13441235192</v>
+        <v>-68259.53774098211</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1328093.302308396</v>
+        <v>-1323385.385510547</v>
       </c>
       <c r="C6" t="n">
-        <v>6698082.425073916</v>
+        <v>6619107.984340863</v>
       </c>
       <c r="D6" t="n">
-        <v>-944168.1705249334</v>
+        <v>-961357.1764391186</v>
       </c>
       <c r="E6" t="n">
-        <v>29325.63041014084</v>
+        <v>51386.665285556</v>
       </c>
       <c r="F6" t="n">
-        <v>632933.8566111278</v>
+        <v>630005.3735070057</v>
       </c>
       <c r="G6" t="n">
-        <v>103152.3496587172</v>
+        <v>101572.7031135229</v>
       </c>
       <c r="H6" t="n">
-        <v>41814.67440470694</v>
+        <v>40450.48670456488</v>
       </c>
       <c r="I6" t="n">
-        <v>-15961.90737157771</v>
+        <v>-19317.72078018319</v>
       </c>
       <c r="J6" t="n">
-        <v>-3578.90421462068</v>
+        <v>-4403.378078683914</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>867122.0012804061</v>
+        <v>1021221.675972942</v>
       </c>
       <c r="C7" t="n">
-        <v>-3603290.722517366</v>
+        <v>-4318637.52309328</v>
       </c>
       <c r="D7" t="n">
-        <v>965194.8779405054</v>
+        <v>1116645.505633131</v>
       </c>
       <c r="E7" t="n">
-        <v>-66211.02352569906</v>
+        <v>-83762.1110364671</v>
       </c>
       <c r="F7" t="n">
-        <v>103152.349674764</v>
+        <v>101572.7031133745</v>
       </c>
       <c r="G7" t="n">
-        <v>64930.12376743408</v>
+        <v>71219.22681444506</v>
       </c>
       <c r="H7" t="n">
-        <v>-69962.77167174855</v>
+        <v>-79943.18277020889</v>
       </c>
       <c r="I7" t="n">
-        <v>205013.4037904658</v>
+        <v>234158.6833005606</v>
       </c>
       <c r="J7" t="n">
-        <v>51392.63156420732</v>
+        <v>58660.81827776847</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2551061.795805831</v>
+        <v>-2869127.226252106</v>
       </c>
       <c r="C8" t="n">
-        <v>7802721.05018572</v>
+        <v>8740901.746992663</v>
       </c>
       <c r="D8" t="n">
-        <v>-2794640.381149374</v>
+        <v>-3148827.625690766</v>
       </c>
       <c r="E8" t="n">
-        <v>-5464.288428942275</v>
+        <v>-5385.102495102625</v>
       </c>
       <c r="F8" t="n">
-        <v>41814.67437393203</v>
+        <v>40450.48670392342</v>
       </c>
       <c r="G8" t="n">
-        <v>-69962.77168035094</v>
+        <v>-79943.18277064641</v>
       </c>
       <c r="H8" t="n">
-        <v>175727.4161489746</v>
+        <v>197211.3457723271</v>
       </c>
       <c r="I8" t="n">
-        <v>-399143.7546658635</v>
+        <v>-450209.4886907187</v>
       </c>
       <c r="J8" t="n">
-        <v>-99404.1887000845</v>
+        <v>-112127.8367041308</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5788454.700806917</v>
+        <v>6563952.749615051</v>
       </c>
       <c r="C9" t="n">
-        <v>-22109850.83148826</v>
+        <v>-25001588.9954452</v>
       </c>
       <c r="D9" t="n">
-        <v>5999557.627929104</v>
+        <v>6832576.364002075</v>
       </c>
       <c r="E9" t="n">
-        <v>-219662.6052052251</v>
+        <v>-278391.2796486993</v>
       </c>
       <c r="F9" t="n">
-        <v>-15961.90729418514</v>
+        <v>-19317.72077972802</v>
       </c>
       <c r="G9" t="n">
-        <v>205013.4038077886</v>
+        <v>234158.6833008617</v>
       </c>
       <c r="H9" t="n">
-        <v>-399143.7546576583</v>
+        <v>-450209.4886895011</v>
       </c>
       <c r="I9" t="n">
-        <v>1002650.592368206</v>
+        <v>1141420.869383243</v>
       </c>
       <c r="J9" t="n">
-        <v>249861.1594954114</v>
+        <v>284455.6521764574</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1441567.158022932</v>
+        <v>1634841.839049607</v>
       </c>
       <c r="C10" t="n">
-        <v>-5495882.108062882</v>
+        <v>-6218125.940521718</v>
       </c>
       <c r="D10" t="n">
-        <v>1494045.406039651</v>
+        <v>1701453.522227231</v>
       </c>
       <c r="E10" t="n">
-        <v>-53578.13441487408</v>
+        <v>-68259.53774289764</v>
       </c>
       <c r="F10" t="n">
-        <v>-3578.904195318219</v>
+        <v>-4403.378078581351</v>
       </c>
       <c r="G10" t="n">
-        <v>51392.63156846038</v>
+        <v>58660.8182778425</v>
       </c>
       <c r="H10" t="n">
-        <v>-99404.18869790898</v>
+        <v>-112127.836703827</v>
       </c>
       <c r="I10" t="n">
-        <v>249861.1594950863</v>
+        <v>284455.6521764575</v>
       </c>
       <c r="J10" t="n">
-        <v>62343.80485054158</v>
+        <v>70968.00317338499</v>
       </c>
     </row>
   </sheetData>
